--- a/启量系统批量脚本工具/dramabagus批量广告工具/data/tasks-dramabagus.xlsx
+++ b/启量系统批量脚本工具/dramabagus批量广告工具/data/tasks-dramabagus.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="108">
   <si>
     <t>任务</t>
   </si>
@@ -106,37 +106,133 @@
     <t>鼎河</t>
   </si>
   <si>
+    <t>7605455941589893136</t>
+  </si>
+  <si>
+    <t>drama</t>
+  </si>
+  <si>
+    <t>千金难买1</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>大-鼎河-千金难买-沪-1</t>
+  </si>
+  <si>
+    <t>千金难买</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>印尼15,印尼14,印尼13,印尼8</t>
+  </si>
+  <si>
+    <t>价值</t>
+  </si>
+  <si>
+    <t>目标ROAS</t>
+  </si>
+  <si>
+    <t>18+</t>
+  </si>
+  <si>
+    <t>7605813091758112785</t>
+  </si>
+  <si>
+    <t>千金难买2</t>
+  </si>
+  <si>
+    <t>大-鼎河-千金难买-沪-2</t>
+  </si>
+  <si>
+    <t>印尼7,印尼6,印尼5,印尼4</t>
+  </si>
+  <si>
+    <t>7625850761410527248</t>
+  </si>
+  <si>
+    <t>大-洋河-千金难买-沪-1</t>
+  </si>
+  <si>
+    <t>印尼3,印尼2,印尼1,印尼31</t>
+  </si>
+  <si>
+    <t>7625850826784391184</t>
+  </si>
+  <si>
+    <t>大-洋河-千金难买-沪-2</t>
+  </si>
+  <si>
+    <t>印尼31,印尼30,印尼29,印尼28</t>
+  </si>
+  <si>
+    <t>我心永恒1</t>
+  </si>
+  <si>
+    <t>大-鼎河-我心永恒-沪-1</t>
+  </si>
+  <si>
+    <t>我心永恒</t>
+  </si>
+  <si>
+    <t>印尼27,印尼26,印尼25,印尼24</t>
+  </si>
+  <si>
+    <t>我心永恒2</t>
+  </si>
+  <si>
+    <t>大-鼎河-我心永恒-沪-2</t>
+  </si>
+  <si>
+    <t>印尼23,印尼22,印尼21,印尼20</t>
+  </si>
+  <si>
+    <t>大-洋河-我心永恒-沪-1</t>
+  </si>
+  <si>
+    <t>印尼19,印尼18,印尼17,印尼16</t>
+  </si>
+  <si>
+    <t>大-洋河-我心永恒-沪-2</t>
+  </si>
+  <si>
+    <t>7605813081117179920</t>
+  </si>
+  <si>
+    <t>大-鼎河-千金难买-鲁-1</t>
+  </si>
+  <si>
+    <t>7605813123773284353</t>
+  </si>
+  <si>
+    <t>大-鼎河-千金难买-鲁-2</t>
+  </si>
+  <si>
+    <t>大-鼎河-我心永恒-鲁-1</t>
+  </si>
+  <si>
+    <t>大-鼎河-我心永恒-鲁-2</t>
+  </si>
+  <si>
     <t>7622891101061414928</t>
   </si>
   <si>
-    <t>drama</t>
-  </si>
-  <si>
     <t>夏天的海风</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>小-鼎河-夏天的海风-赣-6</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>印尼13,印尼14</t>
   </si>
   <si>
-    <t>价值</t>
-  </si>
-  <si>
-    <t>目标ROAS</t>
-  </si>
-  <si>
     <t>02:00:00</t>
   </si>
   <si>
-    <t>18+</t>
+    <t>印尼7,印尼6</t>
   </si>
   <si>
     <t>7622891132078358529</t>
@@ -160,7 +256,7 @@
     <t>转化</t>
   </si>
   <si>
-    <t>成本上限(CPA)</t>
+    <t>最大化投放</t>
   </si>
   <si>
     <t>03:00:00</t>
@@ -169,19 +265,13 @@
     <t>25+</t>
   </si>
   <si>
+    <t>暗夜微光2</t>
+  </si>
+  <si>
     <t>暗夜微光3</t>
   </si>
   <si>
     <t>小-鼎河-你不知死活-赣-5</t>
-  </si>
-  <si>
-    <t>印尼7,印尼6</t>
-  </si>
-  <si>
-    <t>最大化投放</t>
-  </si>
-  <si>
-    <t>暗夜微光2</t>
   </si>
   <si>
     <t>字段说明</t>
@@ -276,13 +366,6 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -307,6 +390,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF375621"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -926,10 +1015,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -937,7 +1026,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -945,9 +1034,8 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -955,7 +1043,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -963,7 +1051,22 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1347,8 +1450,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X5"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="4"/>
+  <dimension ref="A1:X13"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="6.83035714285714" customWidth="1"/>
     <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
@@ -1448,69 +1551,68 @@
       </c>
     </row>
     <row r="2" spans="1:24">
-      <c r="A2">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F2"/>
       <c r="G2" t="s">
         <v>28</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="7">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
+      <c r="J2" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="M2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O2">
-        <v>1.6</v>
-      </c>
-      <c r="P2">
-        <v>120</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>46152</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="N2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S2" t="s">
+      <c r="O2" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P2" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R2" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
@@ -1520,64 +1622,56 @@
       </c>
     </row>
     <row r="3" spans="1:24">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="11" t="s">
         <v>36</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3"/>
+      <c r="E3" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="7">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>27</v>
+      <c r="I3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O3">
-        <v>1.6</v>
-      </c>
-      <c r="P3">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>46152</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="N3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S3" t="s">
+      <c r="O3" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P3" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R3" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
       <c r="W3" t="b">
         <v>0</v>
       </c>
@@ -1585,69 +1679,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="18" spans="1:24">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>25</v>
+    <row r="4" spans="1:24">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4"/>
+      <c r="E4" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K4"/>
+      <c r="J4" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="L4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" t="s">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>150</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>46152</v>
-      </c>
-      <c r="R4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" t="s">
-        <v>30</v>
-      </c>
-      <c r="U4" t="s">
-        <v>30</v>
-      </c>
-      <c r="V4" t="s">
-        <v>30</v>
-      </c>
+      <c r="M4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P4" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R4" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
       <c r="W4" t="b">
         <v>0</v>
       </c>
@@ -1655,62 +1737,510 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="18" spans="1:24">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>36</v>
+    <row r="5" spans="1:24">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>46</v>
+      <c r="E5" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="7">
         <v>1</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>41</v>
+      <c r="I5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>150</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>46152</v>
-      </c>
-      <c r="R5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" t="s">
         <v>45</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P5" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R5" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" s="7">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P6" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R6" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P7" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P8" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R8" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P9" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R9" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P10" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R10" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P11" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R11" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" s="7">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="7">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P12" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R12" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="7">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O13" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="P13" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>46132</v>
+      </c>
+      <c r="R13" s="10">
+        <v>0.159722222222222</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
         <v>2</v>
       </c>
     </row>
@@ -1718,7 +2248,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:X1 A2:A3 H2:H4 K2:K3" numberStoredAsText="1"/>
+    <ignoredError sqref="K2:K3 A1:X1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1833,14 +2363,14 @@
       <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>25</v>
+      <c r="C2" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1849,22 +2379,22 @@
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="4" t="s">
         <v>33</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="O2">
         <v>1.6</v>
@@ -1872,23 +2402,23 @@
       <c r="P2">
         <v>120</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <v>46152</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="S2" t="s">
         <v>35</v>
       </c>
       <c r="T2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
@@ -1902,37 +2432,37 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3">
         <v>1.6</v>
@@ -1941,28 +2471,28 @@
         <v>300</v>
       </c>
       <c r="Q3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -1970,37 +2500,37 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4">
         <v>1.6</v>
@@ -2009,28 +2539,28 @@
         <v>100</v>
       </c>
       <c r="Q4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:24">
@@ -2040,14 +2570,14 @@
       <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>25</v>
+      <c r="C5" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>39</v>
+      <c r="E5" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -2056,19 +2586,19 @@
         <v>1</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>41</v>
+        <v>72</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -2076,23 +2606,23 @@
       <c r="P5">
         <v>150</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="4">
         <v>46152</v>
       </c>
       <c r="R5" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="S5" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="T5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
@@ -2105,40 +2635,40 @@
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>50</v>
+      <c r="C6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>41</v>
+        <v>72</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:24">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>46</v>
+      <c r="C7" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>41</v>
+        <v>80</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2161,16 +2691,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2178,13 +2708,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2192,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2206,13 +2736,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2220,13 +2750,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2234,13 +2764,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2248,13 +2778,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2262,10 +2792,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -2276,13 +2806,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2290,27 +2820,27 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
